--- a/Result/profitability/5520.xlsx
+++ b/Result/profitability/5520.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.77</v>
       </c>
       <c r="M2" t="n">
-        <v>2.21875</v>
+        <v>2.2625</v>
       </c>
       <c r="N2" t="n">
-        <v>20.91875</v>
+        <v>21.07125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.73</v>
       </c>
       <c r="M3" t="n">
-        <v>2.02125</v>
+        <v>2.07625</v>
       </c>
       <c r="N3" t="n">
-        <v>19.7575</v>
+        <v>20.20125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.13</v>
       </c>
       <c r="M4" t="n">
-        <v>1.885</v>
+        <v>1.9175</v>
       </c>
       <c r="N4" t="n">
-        <v>19.14125</v>
+        <v>19.18</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.17</v>
       </c>
       <c r="M5" t="n">
-        <v>1.60625</v>
+        <v>1.58</v>
       </c>
       <c r="N5" t="n">
-        <v>18.03875</v>
+        <v>17.90625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.37875</v>
+        <v>1.38</v>
       </c>
       <c r="N6" t="n">
-        <v>17.2725</v>
+        <v>17.02625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.7</v>
       </c>
       <c r="M7" t="n">
-        <v>1.135</v>
+        <v>1.21125</v>
       </c>
       <c r="N7" t="n">
-        <v>16.41625</v>
+        <v>17.26125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.99</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0025</v>
+        <v>1.025</v>
       </c>
       <c r="N8" t="n">
-        <v>16.71</v>
+        <v>16.535</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.75</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7862499999999999</v>
+        <v>0.78625</v>
       </c>
       <c r="N9" t="n">
         <v>15.49875</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5520</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1023</v>
+      </c>
+      <c r="D75" t="n">
+        <v>783</v>
+      </c>
+      <c r="E75" t="n">
+        <v>240</v>
+      </c>
+      <c r="F75" t="n">
+        <v>23.42</v>
+      </c>
+      <c r="G75" t="n">
+        <v>190</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>18.55%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>10</v>
+      </c>
+      <c r="J75" t="n">
+        <v>199</v>
+      </c>
+      <c r="K75" t="n">
+        <v>159</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.455</v>
+      </c>
+      <c r="N75" t="n">
+        <v>22.49375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1800000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.07258064516129048</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.399999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0564061240934729</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.07317073170731703</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.059999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.0433006535947712</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
